--- a/output/tables/spo2_12h_by_treatment_patient_level.xlsx
+++ b/output/tables/spo2_12h_by_treatment_patient_level.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
   <si>
     <t xml:space="preserve">Time Since Randomisation (hours)
 </t>
@@ -22,6 +22,9 @@
   </si>
   <si>
     <t xml:space="preserve">Welch Two Sample t-test</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Abbreviation: CI = Confidence Interval</t>
   </si>
   <si>
     <t xml:space="preserve">Patients
@@ -102,6 +105,47 @@
   </si>
   <si>
     <t xml:space="preserve">94.22 (2.48)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mean Difference
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95% CI
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-2.72, 0.62</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-3.62, -1.26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-3.91, -1.56</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-3.83, -2.05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-2.91, -1.11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-3.34, -1.10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-3.33, -1.22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-2.55, -0.41</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-2.60, -0.11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-2.43, -0.10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-2.51, 0.17</t>
   </si>
   <si>
     <t xml:space="preserve">p-value
@@ -550,6 +594,8 @@
     <col min="3" max="3" width="10.71" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="10.71" hidden="0" customWidth="1"/>
     <col min="5" max="5" width="10.71" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="10.71" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="10.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="NA" customHeight="1">
@@ -557,16 +603,22 @@
         <v>0</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="2" ht="NA" customHeight="1">
@@ -577,12 +629,18 @@
         <v>58</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E2" s="7" t="n">
+        <v>-1.05</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2" s="7" t="n">
         <v>0.2</v>
       </c>
     </row>
@@ -594,13 +652,19 @@
         <v>58</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="E3" s="8" t="s">
-        <v>29</v>
+        <v>19</v>
+      </c>
+      <c r="E3" s="8" t="n">
+        <v>-2.44</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="G3" s="8" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="4" ht="NA" customHeight="1">
@@ -611,13 +675,19 @@
         <v>58</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>29</v>
+        <v>20</v>
+      </c>
+      <c r="E4" s="8" t="n">
+        <v>-2.73</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="5" ht="NA" customHeight="1">
@@ -628,13 +698,19 @@
         <v>56</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="E5" s="8" t="s">
-        <v>29</v>
+        <v>21</v>
+      </c>
+      <c r="E5" s="8" t="n">
+        <v>-2.94</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="6" ht="NA" customHeight="1">
@@ -645,13 +721,19 @@
         <v>56</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="E6" s="8" t="s">
-        <v>29</v>
+        <v>22</v>
+      </c>
+      <c r="E6" s="8" t="n">
+        <v>-2.01</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="7" ht="NA" customHeight="1">
@@ -662,13 +744,19 @@
         <v>56</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="E7" s="8" t="s">
-        <v>29</v>
+        <v>23</v>
+      </c>
+      <c r="E7" s="8" t="n">
+        <v>-2.22</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="8" ht="NA" customHeight="1">
@@ -679,13 +767,19 @@
         <v>56</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="E8" s="8" t="s">
-        <v>29</v>
+        <v>24</v>
+      </c>
+      <c r="E8" s="8" t="n">
+        <v>-2.27</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="9" ht="NA" customHeight="1">
@@ -696,12 +790,18 @@
         <v>55</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E9" s="8" t="n">
+        <v>-1.48</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="G9" s="8" t="n">
         <v>0.008</v>
       </c>
     </row>
@@ -713,12 +813,18 @@
         <v>54</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E10" s="8" t="n">
+        <v>-1.36</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="G10" s="8" t="n">
         <v>0.033</v>
       </c>
     </row>
@@ -730,12 +836,18 @@
         <v>52</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E11" s="8" t="n">
+        <v>-1.27</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="G11" s="8" t="n">
         <v>0.033</v>
       </c>
     </row>
@@ -747,12 +859,18 @@
         <v>49</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E12" s="9" t="n">
+        <v>-1.17</v>
+      </c>
+      <c r="F12" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="G12" s="9" t="n">
         <v>0.085</v>
       </c>
     </row>
@@ -772,28 +890,64 @@
       <c r="E13" s="5" t="s">
         <v>1</v>
       </c>
+      <c r="F13" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="14" ht="NA" customHeight="1">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="C14" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="D14" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="E14" s="3" t="s">
+      <c r="E14" s="4" t="s">
         <v>2</v>
       </c>
+      <c r="F14" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" ht="NA" customHeight="1">
+      <c r="A15" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A13:E13"/>
-    <mergeCell ref="A14:E14"/>
+  <mergeCells count="3">
+    <mergeCell ref="A13:G13"/>
+    <mergeCell ref="A14:G14"/>
+    <mergeCell ref="A15:G15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/output/tables/spo2_12h_by_treatment_patient_level.xlsx
+++ b/output/tables/spo2_12h_by_treatment_patient_level.xlsx
@@ -21,7 +21,7 @@
     <t xml:space="preserve">Mean (SD)</t>
   </si>
   <si>
-    <t xml:space="preserve">Welch Two Sample t-test</t>
+    <t xml:space="preserve">Wilcoxon rank sum test; Wilcoxon rank sum exact test</t>
   </si>
   <si>
     <t xml:space="preserve">Abbreviation: CI = Confidence Interval</t>
@@ -32,79 +32,79 @@
   </si>
   <si>
     <t xml:space="preserve">Conservative
-N = 28
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.53 (2.49)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.27 (1.71)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.00 (1.82)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.88 (1.59)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.26 (1.39)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.06 (2.06)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.12 (1.96)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.22 (1.77)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.81 (2.33)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.76 (1.99)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.04 (2.16)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Usual care
 N = 30
 </t>
   </si>
   <si>
-    <t xml:space="preserve">94.58 (3.77)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.71 (2.69)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.74 (2.58)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.82 (1.75)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.27 (1.95)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.28 (2.12)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.39 (1.98)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.71 (2.17)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.17 (2.23)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.03 (2.19)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.22 (2.48)</t>
+    <t xml:space="preserve">93.59 (2.44)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.16 (1.71)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.02 (1.77)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.92 (1.64)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.30 (1.51)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.04 (1.99)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.17 (1.92)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.14 (1.79)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.76 (2.33)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.57 (2.04)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.04 (2.11)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Usual care
+N = 35
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.61 (3.59)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.72 (2.58)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.69 (2.57)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.83 (1.70)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.38 (1.96)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.41 (2.32)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.42 (1.95)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.90 (2.24)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.20 (2.26)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.06 (2.13)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.20 (2.63)</t>
   </si>
   <si>
     <t xml:space="preserve">Mean Difference
@@ -115,37 +115,37 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">-2.72, 0.62</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-3.62, -1.26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-3.91, -1.56</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-3.83, -2.05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-2.91, -1.11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-3.34, -1.10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-3.33, -1.22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-2.55, -0.41</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-2.60, -0.11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-2.43, -0.10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-2.51, 0.17</t>
+    <t xml:space="preserve">-2.69, 0.02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-3.73, -1.91</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-4.07, -2.08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-3.91, -2.43</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-3.25, -1.48</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-3.66, -1.36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-3.61, -1.26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-2.93, -0.82</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-2.81, -0.20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-2.87, -0.36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-2.67, 0.19</t>
   </si>
   <si>
     <t xml:space="preserve">p-value
@@ -626,7 +626,7 @@
         <v>-12</v>
       </c>
       <c r="B2" s="7" t="n">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>6</v>
@@ -635,13 +635,13 @@
         <v>18</v>
       </c>
       <c r="E2" s="7" t="n">
-        <v>-1.05</v>
+        <v>-1.46</v>
       </c>
       <c r="F2" s="7" t="s">
         <v>31</v>
       </c>
       <c r="G2" s="7" t="n">
-        <v>0.2</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="3" ht="NA" customHeight="1">
@@ -649,7 +649,7 @@
         <v>0</v>
       </c>
       <c r="B3" s="8" t="n">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="C3" s="8" t="s">
         <v>7</v>
@@ -658,7 +658,7 @@
         <v>19</v>
       </c>
       <c r="E3" s="8" t="n">
-        <v>-2.44</v>
+        <v>-2.92</v>
       </c>
       <c r="F3" s="8" t="s">
         <v>32</v>
@@ -672,7 +672,7 @@
         <v>12</v>
       </c>
       <c r="B4" s="8" t="n">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="C4" s="8" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>20</v>
       </c>
       <c r="E4" s="8" t="n">
-        <v>-2.73</v>
+        <v>-3.09</v>
       </c>
       <c r="F4" s="8" t="s">
         <v>33</v>
@@ -695,7 +695,7 @@
         <v>24</v>
       </c>
       <c r="B5" s="8" t="n">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="C5" s="8" t="s">
         <v>9</v>
@@ -704,7 +704,7 @@
         <v>21</v>
       </c>
       <c r="E5" s="8" t="n">
-        <v>-2.94</v>
+        <v>-3.27</v>
       </c>
       <c r="F5" s="8" t="s">
         <v>34</v>
@@ -718,7 +718,7 @@
         <v>36</v>
       </c>
       <c r="B6" s="8" t="n">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="C6" s="8" t="s">
         <v>10</v>
@@ -727,7 +727,7 @@
         <v>22</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>-2.01</v>
+        <v>-2.44</v>
       </c>
       <c r="F6" s="8" t="s">
         <v>35</v>
@@ -741,7 +741,7 @@
         <v>48</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="C7" s="8" t="s">
         <v>11</v>
@@ -750,7 +750,7 @@
         <v>23</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>-2.22</v>
+        <v>-2.58</v>
       </c>
       <c r="F7" s="8" t="s">
         <v>36</v>
@@ -764,7 +764,7 @@
         <v>60</v>
       </c>
       <c r="B8" s="8" t="n">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="C8" s="8" t="s">
         <v>12</v>
@@ -773,7 +773,7 @@
         <v>24</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>-2.27</v>
+        <v>-2.47</v>
       </c>
       <c r="F8" s="8" t="s">
         <v>37</v>
@@ -787,7 +787,7 @@
         <v>72</v>
       </c>
       <c r="B9" s="8" t="n">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="C9" s="8" t="s">
         <v>13</v>
@@ -796,13 +796,13 @@
         <v>25</v>
       </c>
       <c r="E9" s="8" t="n">
-        <v>-1.48</v>
+        <v>-1.96</v>
       </c>
       <c r="F9" s="8" t="s">
         <v>38</v>
       </c>
       <c r="G9" s="8" t="n">
-        <v>0.008</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="10" ht="NA" customHeight="1">
@@ -810,7 +810,7 @@
         <v>84</v>
       </c>
       <c r="B10" s="8" t="n">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="C10" s="8" t="s">
         <v>14</v>
@@ -819,13 +819,13 @@
         <v>26</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>-1.36</v>
+        <v>-1.54</v>
       </c>
       <c r="F10" s="8" t="s">
         <v>39</v>
       </c>
       <c r="G10" s="8" t="n">
-        <v>0.033</v>
+        <v>0.023</v>
       </c>
     </row>
     <row r="11" ht="NA" customHeight="1">
@@ -833,7 +833,7 @@
         <v>96</v>
       </c>
       <c r="B11" s="8" t="n">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="C11" s="8" t="s">
         <v>15</v>
@@ -842,13 +842,13 @@
         <v>27</v>
       </c>
       <c r="E11" s="8" t="n">
-        <v>-1.27</v>
+        <v>-1.6</v>
       </c>
       <c r="F11" s="8" t="s">
         <v>40</v>
       </c>
       <c r="G11" s="8" t="n">
-        <v>0.033</v>
+        <v>0.011</v>
       </c>
     </row>
     <row r="12" ht="NA" customHeight="1">
@@ -856,7 +856,7 @@
         <v>108</v>
       </c>
       <c r="B12" s="9" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C12" s="9" t="s">
         <v>16</v>
@@ -865,13 +865,13 @@
         <v>28</v>
       </c>
       <c r="E12" s="9" t="n">
-        <v>-1.17</v>
+        <v>-1.27</v>
       </c>
       <c r="F12" s="9" t="s">
         <v>41</v>
       </c>
       <c r="G12" s="9" t="n">
-        <v>0.085</v>
+        <v>0.069</v>
       </c>
     </row>
     <row r="13" ht="NA" customHeight="1">

--- a/output/tables/spo2_12h_by_treatment_patient_level.xlsx
+++ b/output/tables/spo2_12h_by_treatment_patient_level.xlsx
@@ -18,15 +18,6 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Mean (SD)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wilcoxon rank sum test; Wilcoxon rank sum exact test</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Abbreviation: CI = Confidence Interval</t>
-  </si>
-  <si>
     <t xml:space="preserve">Patients
 </t>
   </si>
@@ -36,77 +27,11 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">93.59 (2.44)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.16 (1.71)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.02 (1.77)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.92 (1.64)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.30 (1.51)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.04 (1.99)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.17 (1.92)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.14 (1.79)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.76 (2.33)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.57 (2.04)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.04 (2.11)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Usual care
 N = 35
 </t>
   </si>
   <si>
-    <t xml:space="preserve">94.61 (3.59)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.72 (2.58)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.69 (2.57)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.83 (1.70)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.38 (1.96)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.41 (2.32)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.42 (1.95)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.90 (2.24)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.20 (2.26)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.06 (2.13)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.20 (2.63)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Mean Difference
 </t>
   </si>
@@ -115,44 +40,119 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">-2.69, 0.02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-3.73, -1.91</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-4.07, -2.08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-3.91, -2.43</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-3.25, -1.48</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-3.66, -1.36</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-3.61, -1.26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-2.93, -0.82</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-2.81, -0.20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-2.87, -0.36</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-2.67, 0.19</t>
-  </si>
-  <si>
     <t xml:space="preserve">p-value
 </t>
   </si>
   <si>
+    <t xml:space="preserve">92.78 (1.74)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.75 (2.62)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-3.21, -1.42</t>
+  </si>
+  <si>
     <t xml:space="preserve">&lt;0.001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.18 (1.10)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.71 (1.66)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-3.67, -1.65</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.00 (2.04)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.92 (1.68)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-4.37, -1.63</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.14 (1.38)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.61 (1.83)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-3.62, -1.60</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.04 (1.69)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.08 (1.79)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-3.54, -0.69</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.08 (1.86)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.23 (2.11)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-4.16, -0.53</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.35 (1.43)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.80 (1.40)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-2.60, -0.24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.65 (2.20)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.88 (2.15)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-3.14, 0.63</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.64 (1.66)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.32 (1.99)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-3.29, -0.31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.63 (1.91)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.48 (2.55)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-2.67, 1.20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.59 (2.37)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.10 (1.82)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-3.36, 0.48</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mean (SD)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wilcoxon rank sum exact test; Wilcoxon rank sum test</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Abbreviation: CI = Confidence Interval</t>
   </si>
 </sst>
 </file>
@@ -603,22 +603,22 @@
         <v>0</v>
       </c>
       <c r="B1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="F1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="D1" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="E1" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="F1" s="6" t="s">
-        <v>30</v>
-      </c>
       <c r="G1" s="6" t="s">
-        <v>42</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2" ht="NA" customHeight="1">
@@ -626,22 +626,22 @@
         <v>-12</v>
       </c>
       <c r="B2" s="7" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E2" s="7" t="n">
-        <v>-1.46</v>
+        <v>-2.3</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="G2" s="7" t="n">
-        <v>0.06</v>
+        <v>9</v>
+      </c>
+      <c r="G2" s="7" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="3" ht="NA" customHeight="1">
@@ -649,22 +649,22 @@
         <v>0</v>
       </c>
       <c r="B3" s="8" t="n">
-        <v>64</v>
+        <v>34</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E3" s="8" t="n">
-        <v>-2.92</v>
+        <v>-2.59</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>43</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" ht="NA" customHeight="1">
@@ -672,22 +672,22 @@
         <v>12</v>
       </c>
       <c r="B4" s="8" t="n">
-        <v>65</v>
+        <v>29</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E4" s="8" t="n">
-        <v>-3.09</v>
+        <v>-3.35</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>43</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" ht="NA" customHeight="1">
@@ -695,22 +695,22 @@
         <v>24</v>
       </c>
       <c r="B5" s="8" t="n">
-        <v>63</v>
+        <v>34</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E5" s="8" t="n">
-        <v>-3.27</v>
+        <v>-2.86</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>43</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" ht="NA" customHeight="1">
@@ -718,22 +718,22 @@
         <v>36</v>
       </c>
       <c r="B6" s="8" t="n">
-        <v>63</v>
+        <v>29</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D6" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E6" s="8" t="n">
+        <v>-2.38</v>
+      </c>
+      <c r="F6" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="E6" s="8" t="n">
-        <v>-2.44</v>
-      </c>
-      <c r="F6" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="G6" s="8" t="s">
-        <v>43</v>
+      <c r="G6" s="8" t="n">
+        <v>0.003</v>
       </c>
     </row>
     <row r="7" ht="NA" customHeight="1">
@@ -741,22 +741,22 @@
         <v>48</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>63</v>
+        <v>34</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>-2.58</v>
+        <v>-2.35</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="G7" s="8" t="s">
-        <v>43</v>
+        <v>25</v>
+      </c>
+      <c r="G7" s="8" t="n">
+        <v>0.004</v>
       </c>
     </row>
     <row r="8" ht="NA" customHeight="1">
@@ -764,22 +764,22 @@
         <v>60</v>
       </c>
       <c r="B8" s="8" t="n">
-        <v>63</v>
+        <v>29</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>-2.47</v>
+        <v>-1.57</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="G8" s="8" t="s">
-        <v>43</v>
+        <v>28</v>
+      </c>
+      <c r="G8" s="8" t="n">
+        <v>0.009</v>
       </c>
     </row>
     <row r="9" ht="NA" customHeight="1">
@@ -787,22 +787,22 @@
         <v>72</v>
       </c>
       <c r="B9" s="8" t="n">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E9" s="8" t="n">
-        <v>-1.96</v>
+        <v>-1.73</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="G9" s="8" t="n">
-        <v>0.001</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="10" ht="NA" customHeight="1">
@@ -810,22 +810,22 @@
         <v>84</v>
       </c>
       <c r="B10" s="8" t="n">
-        <v>61</v>
+        <v>28</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>-1.54</v>
+        <v>-1.78</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="G10" s="8" t="n">
-        <v>0.023</v>
+        <v>0.033</v>
       </c>
     </row>
     <row r="11" ht="NA" customHeight="1">
@@ -833,22 +833,22 @@
         <v>96</v>
       </c>
       <c r="B11" s="8" t="n">
-        <v>59</v>
+        <v>26</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="E11" s="8" t="n">
-        <v>-1.6</v>
+        <v>-0.85</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G11" s="8" t="n">
-        <v>0.011</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="12" ht="NA" customHeight="1">
@@ -856,91 +856,91 @@
         <v>108</v>
       </c>
       <c r="B12" s="9" t="n">
-        <v>52</v>
+        <v>24</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="E12" s="9" t="n">
-        <v>-1.27</v>
+        <v>-1.66</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G12" s="9" t="n">
-        <v>0.069</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="13" ht="NA" customHeight="1">
       <c r="A13" s="5" t="s">
-        <v>1</v>
+        <v>41</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>1</v>
+        <v>41</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>1</v>
+        <v>41</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>1</v>
+        <v>41</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>1</v>
+        <v>41</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>1</v>
+        <v>41</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>1</v>
+        <v>41</v>
       </c>
     </row>
     <row r="14" ht="NA" customHeight="1">
       <c r="A14" s="4" t="s">
-        <v>2</v>
+        <v>42</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>2</v>
+        <v>42</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>2</v>
+        <v>42</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>2</v>
+        <v>42</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>2</v>
+        <v>42</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>2</v>
+        <v>42</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>2</v>
+        <v>42</v>
       </c>
     </row>
     <row r="15" ht="NA" customHeight="1">
       <c r="A15" s="5" t="s">
-        <v>3</v>
+        <v>43</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>3</v>
+        <v>43</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>3</v>
+        <v>43</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>3</v>
+        <v>43</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>3</v>
+        <v>43</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>3</v>
+        <v>43</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>3</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>

--- a/output/tables/spo2_12h_by_treatment_patient_level.xlsx
+++ b/output/tables/spo2_12h_by_treatment_patient_level.xlsx
@@ -44,112 +44,112 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">92.78 (1.74)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.75 (2.62)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-3.21, -1.42</t>
+    <t xml:space="preserve">93.56 (2.43)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.53 (3.57)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-2.59, 0.08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.16 (1.71)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.73 (2.55)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-3.72, -1.94</t>
   </si>
   <si>
     <t xml:space="preserve">&lt;0.001</t>
   </si>
   <si>
-    <t xml:space="preserve">92.18 (1.10)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.71 (1.66)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-3.67, -1.65</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.00 (2.04)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.92 (1.68)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-4.37, -1.63</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.14 (1.38)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.61 (1.83)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-3.62, -1.60</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.04 (1.69)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.08 (1.79)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-3.54, -0.69</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.08 (1.86)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.23 (2.11)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-4.16, -0.53</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.35 (1.43)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.80 (1.40)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-2.60, -0.24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.65 (2.20)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.88 (2.15)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-3.14, 0.63</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.64 (1.66)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.32 (1.99)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-3.29, -0.31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.63 (1.91)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.48 (2.55)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-2.67, 1.20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.59 (2.37)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.10 (1.82)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-3.36, 0.48</t>
+    <t xml:space="preserve">92.02 (1.77)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.68 (2.57)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-4.04, -2.08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.92 (1.64)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.77 (1.69)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-3.81, -2.34</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.30 (1.51)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.31 (1.89)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-3.18, -1.43</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.04 (1.99)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.32 (2.22)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-3.54, -1.33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.17 (1.92)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.30 (1.95)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-3.43, -1.16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.14 (1.79)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.75 (2.00)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-2.78, -0.78</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.76 (2.33)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.06 (2.12)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-2.64, -0.12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.57 (2.04)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.97 (2.04)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-2.79, -0.28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.04 (2.11)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.08 (2.53)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-2.41, 0.25</t>
   </si>
   <si>
     <t xml:space="preserve">Mean (SD)</t>
   </si>
   <si>
-    <t xml:space="preserve">Wilcoxon rank sum exact test; Wilcoxon rank sum test</t>
+    <t xml:space="preserve">Wilcoxon rank sum test; Wilcoxon rank sum exact test</t>
   </si>
   <si>
     <t xml:space="preserve">Abbreviation: CI = Confidence Interval</t>
@@ -635,13 +635,13 @@
         <v>8</v>
       </c>
       <c r="E2" s="7" t="n">
-        <v>-2.3</v>
+        <v>-1.4</v>
       </c>
       <c r="F2" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="7" t="s">
-        <v>10</v>
+      <c r="G2" s="7" t="n">
+        <v>0.071</v>
       </c>
     </row>
     <row r="3" ht="NA" customHeight="1">
@@ -649,22 +649,22 @@
         <v>0</v>
       </c>
       <c r="B3" s="8" t="n">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="C3" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="E3" s="8" t="n">
+        <v>-2.93</v>
+      </c>
+      <c r="F3" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="8" t="n">
-        <v>-2.59</v>
-      </c>
-      <c r="F3" s="8" t="s">
+      <c r="G3" s="8" t="s">
         <v>13</v>
-      </c>
-      <c r="G3" s="8" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="4" ht="NA" customHeight="1">
@@ -672,7 +672,7 @@
         <v>12</v>
       </c>
       <c r="B4" s="8" t="n">
-        <v>29</v>
+        <v>65</v>
       </c>
       <c r="C4" s="8" t="s">
         <v>14</v>
@@ -681,13 +681,13 @@
         <v>15</v>
       </c>
       <c r="E4" s="8" t="n">
-        <v>-3.35</v>
+        <v>-3.09</v>
       </c>
       <c r="F4" s="8" t="s">
         <v>16</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" ht="NA" customHeight="1">
@@ -695,7 +695,7 @@
         <v>24</v>
       </c>
       <c r="B5" s="8" t="n">
-        <v>34</v>
+        <v>63</v>
       </c>
       <c r="C5" s="8" t="s">
         <v>17</v>
@@ -704,13 +704,13 @@
         <v>18</v>
       </c>
       <c r="E5" s="8" t="n">
-        <v>-2.86</v>
+        <v>-3.18</v>
       </c>
       <c r="F5" s="8" t="s">
         <v>19</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" ht="NA" customHeight="1">
@@ -718,7 +718,7 @@
         <v>36</v>
       </c>
       <c r="B6" s="8" t="n">
-        <v>29</v>
+        <v>63</v>
       </c>
       <c r="C6" s="8" t="s">
         <v>20</v>
@@ -732,8 +732,8 @@
       <c r="F6" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="G6" s="8" t="n">
-        <v>0.003</v>
+      <c r="G6" s="8" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="7" ht="NA" customHeight="1">
@@ -741,7 +741,7 @@
         <v>48</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>34</v>
+        <v>63</v>
       </c>
       <c r="C7" s="8" t="s">
         <v>23</v>
@@ -750,13 +750,13 @@
         <v>24</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>-2.35</v>
+        <v>-2.5</v>
       </c>
       <c r="F7" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="G7" s="8" t="n">
-        <v>0.004</v>
+      <c r="G7" s="8" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="8" ht="NA" customHeight="1">
@@ -764,7 +764,7 @@
         <v>60</v>
       </c>
       <c r="B8" s="8" t="n">
-        <v>29</v>
+        <v>63</v>
       </c>
       <c r="C8" s="8" t="s">
         <v>26</v>
@@ -773,13 +773,13 @@
         <v>27</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>-1.57</v>
+        <v>-2.34</v>
       </c>
       <c r="F8" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="G8" s="8" t="n">
-        <v>0.009</v>
+      <c r="G8" s="8" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="9" ht="NA" customHeight="1">
@@ -787,7 +787,7 @@
         <v>72</v>
       </c>
       <c r="B9" s="8" t="n">
-        <v>33</v>
+        <v>62</v>
       </c>
       <c r="C9" s="8" t="s">
         <v>29</v>
@@ -796,13 +796,13 @@
         <v>30</v>
       </c>
       <c r="E9" s="8" t="n">
-        <v>-1.73</v>
+        <v>-1.83</v>
       </c>
       <c r="F9" s="8" t="s">
         <v>31</v>
       </c>
       <c r="G9" s="8" t="n">
-        <v>0.2</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="10" ht="NA" customHeight="1">
@@ -810,7 +810,7 @@
         <v>84</v>
       </c>
       <c r="B10" s="8" t="n">
-        <v>28</v>
+        <v>61</v>
       </c>
       <c r="C10" s="8" t="s">
         <v>32</v>
@@ -819,7 +819,7 @@
         <v>33</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>-1.78</v>
+        <v>-1.4</v>
       </c>
       <c r="F10" s="8" t="s">
         <v>34</v>
@@ -833,7 +833,7 @@
         <v>96</v>
       </c>
       <c r="B11" s="8" t="n">
-        <v>26</v>
+        <v>59</v>
       </c>
       <c r="C11" s="8" t="s">
         <v>35</v>
@@ -842,13 +842,13 @@
         <v>36</v>
       </c>
       <c r="E11" s="8" t="n">
-        <v>-0.85</v>
+        <v>-1.56</v>
       </c>
       <c r="F11" s="8" t="s">
         <v>37</v>
       </c>
       <c r="G11" s="8" t="n">
-        <v>0.5</v>
+        <v>0.014</v>
       </c>
     </row>
     <row r="12" ht="NA" customHeight="1">
@@ -856,7 +856,7 @@
         <v>108</v>
       </c>
       <c r="B12" s="9" t="n">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="C12" s="9" t="s">
         <v>38</v>
@@ -865,13 +865,13 @@
         <v>39</v>
       </c>
       <c r="E12" s="9" t="n">
-        <v>-1.66</v>
+        <v>-1.16</v>
       </c>
       <c r="F12" s="9" t="s">
         <v>40</v>
       </c>
       <c r="G12" s="9" t="n">
-        <v>0.12</v>
+        <v>0.084</v>
       </c>
     </row>
     <row r="13" ht="NA" customHeight="1">
